--- a/reports/meta_intel_2026-W21.xlsx
+++ b/reports/meta_intel_2026-W21.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/meta_intel_2026-W21.xlsx
+++ b/reports/meta_intel_2026-W21.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/meta_intel_2026-W21.xlsx
+++ b/reports/meta_intel_2026-W21.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -557,17 +557,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Keepsake</t>
+          <t>Tellmel</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -577,17 +577,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meminto</t>
+          <t>Keepsake</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>StoryWorth</t>
+          <t>Meminto</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -597,7 +597,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tellmel</t>
+          <t>StoryWorth</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>944701718393132</t>
+          <t>1501005738186114</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1501005738186114</t>
+          <t>1985079728773317</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -875,12 +875,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -905,7 +900,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1985079728773317</t>
+          <t>940930155514923</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -940,7 +935,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940930155514923</t>
+          <t>1701124344229972</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -950,7 +945,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1701124344229972</t>
+          <t>1639743033742217</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -985,12 +985,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Everyone loves stories. Preserving your family's stories shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1015,22 +1010,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4435145500031851</t>
+          <t>1282383093577411</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Actor Cara AnnMarie with Remento</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Con Remento, preservar historias valiosas es tan fácil como tener una conversación. Ellos simplemente hablan, y Remento hace el resto: convierte sus palabras en historias escritas profesionalmente. Cada historia incluye un código QR que, al escanearlo, te lleva a las grabaciones originales. Así puedes verlos o escucharlos cuando quieras, contándote su historia. 👆 Elige preguntas o fotos para inspirar las historias 📱 Graba las respuestas habladas</t>
+          <t>For only $99 you get: 📝 No-Write Biographer Service 📘 Hardcover Memoir (in color!)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>📖 Remento convierte las grabaciones en un libro lleno de historias escritas</t>
+          <t>🧠 Digital Family Memory Hub</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1055,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1639743033742217</t>
+          <t>4525953724345514</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1065,7 +1060,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Everyone loves stories. Preserving your family's stories shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1090,7 +1085,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1282383093577411</t>
+          <t>2028325661366433</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1100,12 +1095,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>For only $99 you get: 📝 No-Write Biographer Service 📘 Hardcover Memoir (in color!)</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🧠 Digital Family Memory Hub</t>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1130,17 +1125,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4525953724345514</t>
+          <t>852962227868306</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>IG mamadefour with Remento</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>Todos tenemos historias que merecen ser contadas… y ahora pueden vivir para siempre. Le regalé a mi papá algo único: su propio libro de memorias hecho con @getremento. Remento aparecio en Shark Tank y funciona asi, te manda preguntas, grabás tus respuestas en video, y la plataforma convierte esa grabación en texto automáticamente.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1165,22 +1160,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2028325661366433</t>
+          <t>4305501549596110</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Actor Cara AnnMarie with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1200,31 +1195,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>852962227868306</t>
+          <t>1868277354563662</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IG mamadefour with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Todos tenemos historias que merecen ser contadas… y ahora pueden vivir para siempre. Le regalé a mi papá algo único: su propio libro de memorias hecho con @getremento. Remento aparecio en Shark Tank y funciona asi, te manda preguntas, grabás tus respuestas en video, y la plataforma convierte esa grabación en texto automáticamente.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1235,36 +1235,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4305501549596110</t>
+          <t>1362684515702149</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1868277354563662</t>
+          <t>1938930663325095</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1362684515702149</t>
+          <t>1852060685669387</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1340,11 +1340,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1938930663325095</t>
+          <t>841302105060560</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1852060685669387</t>
+          <t>1296748252140081</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>841302105060560</t>
+          <t>1588345672369492</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1460,11 +1460,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1296748252140081</t>
+          <t>3976129939359406</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1588345672369492</t>
+          <t>1177236264536592</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1540,11 +1540,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3976129939359406</t>
+          <t>966816482430409</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1580,11 +1580,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1177236264536592</t>
+          <t>1943193019573119</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1620,11 +1620,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>966816482430409</t>
+          <t>4072587919646468</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1660,11 +1660,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1943193019573119</t>
+          <t>2260190851070799</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1700,11 +1700,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4072587919646468</t>
+          <t>1630159098158899</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1730,21 +1730,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2260190851070799</t>
+          <t>796404973298946</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1780,11 +1780,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1630159098158899</t>
+          <t>933151279692839</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1810,21 +1810,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>796404973298946</t>
+          <t>3727759467519562</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>933151279692839</t>
+          <t>850477457839087</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1890,21 +1890,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach Oma &amp; Opa glücklich!🫶 ➡️ Jetzt 120€ sparen! (Gilt nur für kurze Zeit) Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1920,7 +1925,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3727759467519562</t>
+          <t>1549478262721918</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1940,11 +1945,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1960,7 +1965,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>850477457839087</t>
+          <t>2040130603507445</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1970,17 +1975,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mach Oma &amp; Opa glücklich!🫶 ➡️ Jetzt 120€ sparen! (Gilt nur für kurze Zeit) Sorry, we're having trouble playing this video.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1549478262721918</t>
+          <t>1171548231746967</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2025,11 +2025,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2040130603507445</t>
+          <t>871339118687590</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2065,11 +2065,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1171548231746967</t>
+          <t>2761672647588250</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2105,11 +2105,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>871339118687590</t>
+          <t>3888948801242426</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2145,11 +2145,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2761672647588250</t>
+          <t>1196762821852142</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2175,21 +2175,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>⭐️ 4,7 Sterne Bewertung</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Learn More</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2205,7 +2210,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3888948801242426</t>
+          <t>1373162224393589</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2215,7 +2220,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2225,11 +2230,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2245,7 +2250,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1196762821852142</t>
+          <t>2393916927736067</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2255,26 +2260,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>⭐️ 4,7 Sterne Bewertung</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Learn More</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1373162224393589</t>
+          <t>804595359053733</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2310,11 +2310,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2393916927736067</t>
+          <t>1896813954581984</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2350,11 +2350,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>804595359053733</t>
+          <t>4246986475583692</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2405,36 +2405,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1896813954581984</t>
+          <t>1652739722437976</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>192</v>
+        <v>11</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2445,36 +2445,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>1604340910795794</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1652739722437976</t>
+          <t>1907813709863061</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2500,21 +2500,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1604340910795794</t>
+          <t>986777303695569</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1907813709863061</t>
+          <t>830570699644006</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2590,11 +2590,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>986777303695569</t>
+          <t>1342635554344428</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2625,16 +2625,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>830570699644006</t>
+          <t>792414230413551</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2660,21 +2660,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Turn memories into a lasting keepsake</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1342635554344428</t>
+          <t>943864791615557</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>792414230413551</t>
+          <t>977072525149646</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2740,21 +2740,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2770,7 +2775,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>943864791615557</t>
+          <t>2460360471077841</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2780,7 +2785,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2788,13 +2793,18 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2810,7 +2820,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>977072525149646</t>
+          <t>2181963129245755</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2820,12 +2830,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
+          <t>She has stories you've never even heard. Here's how to finally get them into a book. →</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2835,11 +2840,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2855,7 +2860,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2460360471077841</t>
+          <t>1680810166448399</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2865,26 +2870,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2181963129245755</t>
+          <t>1107552519108914</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2910,21 +2910,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>She has stories you've never even heard. Here's how to finally get them into a book. →</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1680810166448399</t>
+          <t>991000993265523</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1107552519108914</t>
+          <t>4209711686009806</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>991000993265523</t>
+          <t>1510732740710867</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Preserve their stories, and their voice, in a book that lasts generations. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3038,13 +3038,18 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3060,7 +3065,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4209711686009806</t>
+          <t>984361874565809</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3070,21 +3075,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3100,7 +3105,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1510732740710867</t>
+          <t>1009981694791489</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3110,7 +3115,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Preserve their stories, and their voice, in a book that lasts generations. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3118,18 +3123,13 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>984361874565809</t>
+          <t>2461937354277318</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3155,21 +3155,21 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Turn memories into a lasting keepsake</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1009981694791489</t>
+          <t>1816986676349316</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2461937354277318</t>
+          <t>1613608029697579</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3240,16 +3240,16 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3260,36 +3260,36 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>Tellmel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1816986676349316</t>
+          <t>1326709665998121</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>TellMel Mental Health Pllc.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Do you need a provider that will actually listen and HEAR you? That's me! I’d love to connect and support those who may benefit from compassionate psychiatric medication management and supportive therapy. Low impression count TellMel Mental Health Pllc.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>Ad Library APIAbout ads and data usePrivacyTermsCookies</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3300,36 +3300,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>Keepsake</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1613608029697579</t>
+          <t>1797082684484054</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>Keepsake Frames</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>In 5 minutes order your photos printed, framed, and shipped to your doorstep. ITUNES.APPLE.COM Keepsake: Your Photos Printed &amp; Framed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Keepsake: Your Photos Printed &amp; Framed</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Install now</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3340,41 +3345,41 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Keepsake</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1797082684484054</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Keepsake Frames</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>In 5 minutes order your photos printed, framed, and shipped to your doorstep. ITUNES.APPLE.COM Keepsake: Your Photos Printed &amp; Framed</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Keepsake: Your Photos Printed &amp; Framed</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Install now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>363</v>
+        <v>46</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3390,7 +3395,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1685628942752739</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3415,11 +3420,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1688004719222897</t>
+          <t>1657931948555000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3445,26 +3450,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1657931948555000</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3490,21 +3490,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3520,7 +3525,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2082672142583809</t>
+          <t>1643835923556092</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3545,11 +3550,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3565,7 +3570,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1643835923556092</t>
+          <t>952068907735194</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3590,11 +3595,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>952068907735194</t>
+          <t>1885769545476096</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3620,7 +3625,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it free today by your local Area Agency on Aging or your Medicaid provider. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3635,11 +3640,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3655,7 +3660,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1885769545476096</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3665,7 +3670,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A digital care companion designed for healthy, happy aging at home. Get it free today by your local Area Agency on Aging or your Medicaid provider. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3680,11 +3685,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3700,7 +3705,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1682907829804633</t>
+          <t>2052874168989707</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3710,26 +3715,21 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it at no cost today by the Area Agency on Aging of Broward County. Check you eligibility today at ElliQ.com/free Apply for a free ElliQ today!</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Get it free today</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2052874168989707</t>
+          <t>1773179040333547</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3755,21 +3755,21 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A digital care companion designed for healthy, happy aging at home. Get it at no cost today by the Area Agency on Aging of Broward County. Check you eligibility today at ElliQ.com/free Apply for a free ElliQ today!</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Get it free today</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1773179040333547</t>
+          <t>1989000975326385</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3795,21 +3795,21 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1989000975326385</t>
+          <t>2903214430021771</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3835,21 +3835,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2903214430021771</t>
+          <t>26725379713817682</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3875,21 +3875,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/DSHS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26725379713817682</t>
+          <t>2534647506933041</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/DSHS</t>
+          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/free</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3925,53 +3925,13 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2534647506933041</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/free</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>45</v>
-      </c>
-      <c r="J81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3988,7 +3948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -4005,7 +3965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>
@@ -4024,7 +3984,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -4034,7 +3994,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7"/>
@@ -4048,47 +4008,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1643835923556092</t>
+          <t>1326709665998121</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1907813709863061</t>
+          <t>1643835923556092</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1989000975326385</t>
+          <t>1907813709863061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2461937354277318</t>
+          <t>1989000975326385</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2903214430021771</t>
+          <t>2461937354277318</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>2903214430021771</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>4246986475583692</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>984361874565809</t>
         </is>

--- a/reports/meta_intel_2026-W21.xlsx
+++ b/reports/meta_intel_2026-W21.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -500,7 +500,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1342635554344428</t>
+          <t>792414230413551</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2625,16 +2625,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>792414230413551</t>
+          <t>943864791615557</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2670,11 +2670,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>943864791615557</t>
+          <t>977072525149646</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2700,21 +2700,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2730,7 +2735,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>977072525149646</t>
+          <t>2460360471077841</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2740,17 +2745,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2759,7 +2764,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2775,7 +2780,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2460360471077841</t>
+          <t>2181963129245755</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2785,26 +2790,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>She has stories you've never even heard. Here's how to finally get them into a book. →</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2181963129245755</t>
+          <t>1680810166448399</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2830,21 +2830,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>She has stories you've never even heard. Here's how to finally get them into a book. →</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1680810166448399</t>
+          <t>1107552519108914</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1107552519108914</t>
+          <t>991000993265523</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>991000993265523</t>
+          <t>4209711686009806</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4209711686009806</t>
+          <t>1521599959561340</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2995,16 +2995,16 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Do you need a provider that will actually listen and HEAR you? That's me! I’d love to connect and support those who may benefit from compassionate psychiatric medication management and supportive therapy. Low impression count TellMel Mental Health Pllc.</t>
+          <t>Do you need a provider that will actually listen and HEAR you? That's me! I’d love to connect and support those who may benefit from compassionate psychiatric medication management and supportive therapy. TellMel Mental Health Pllc. Ad Library APIAbout ads and data usePrivacyTermsCookies</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ad Library APIAbout ads and data usePrivacyTermsCookies</t>
+          <t>Meta © 2026 | English (US)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3929,9 +3929,54 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>944975184903429</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>34</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3948,7 +3993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3965,7 +4010,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3994,7 +4039,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7"/>
@@ -4015,47 +4060,61 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1643835923556092</t>
+          <t>1521599959561340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1907813709863061</t>
+          <t>1643835923556092</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1989000975326385</t>
+          <t>1907813709863061</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2461937354277318</t>
+          <t>1989000975326385</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2903214430021771</t>
+          <t>2461937354277318</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>2903214430021771</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>4246986475583692</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>944975184903429</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>984361874565809</t>
         </is>
